--- a/Pricing Logic/modules/uploads/module_4_702.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_702.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,46 +37,10 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>لبن جهينة كامل الدسم - 1 لتر</t>
-  </si>
-  <si>
-    <t>شويبس ليمون نعناع - 950 مل</t>
-  </si>
-  <si>
-    <t>شويبس جولد اناناس - 300 مل</t>
-  </si>
-  <si>
-    <t>شويبس جولد اناناس - 1.75 لتر</t>
-  </si>
-  <si>
-    <t>شويبس ليمون نعناع جيب - 240 مل</t>
-  </si>
-  <si>
-    <t>شويبس رمان - 950 مل</t>
-  </si>
-  <si>
-    <t>سبيرو سباتيس صودا ليمون - 330 مل</t>
-  </si>
-  <si>
-    <t>سبيرو سباتيس يوسفي - 330 مل</t>
-  </si>
-  <si>
-    <t>سبيرو سباتيس اناناس - 330 مل</t>
-  </si>
-  <si>
-    <t>شويبس يوسفى بلاستيك - 250 مل</t>
-  </si>
-  <si>
-    <t>سبيرو سباتس كولا - 330 جم</t>
-  </si>
-  <si>
-    <t>سبيرو سباتس كانز يوسفى - 330 مل</t>
-  </si>
-  <si>
-    <t>سبيرو سباتس كانز كولا - 330 مل</t>
-  </si>
-  <si>
-    <t>سبيرو سباتس كانز ليمون ليمون صودا- 330 مل</t>
+    <t>بليزو ويفر محشو بالشوكولاتة مغطي بالكراميل و الكرسب و الشوكولاتة بليزو جولد - 10 جنية</t>
+  </si>
+  <si>
+    <t>زيووو اراميش بافس جبنة - 5 جنية</t>
   </si>
   <si>
     <t>YES</t>
@@ -437,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -465,240 +429,53 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>248</v>
+        <v>10816</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>540</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>378</v>
+        <v>10816</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>160</v>
+        <v>564</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>1656</v>
+        <v>12350</v>
       </c>
       <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>49.5</v>
+      </c>
+      <c r="E4" t="s">
         <v>9</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>320</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>2327</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>223</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>5490</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>285</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>8650</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>160</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>9965</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>109</v>
-      </c>
-      <c r="E8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>9967</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="D9">
-        <v>109</v>
-      </c>
-      <c r="E9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>9971</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10">
-        <v>2</v>
-      </c>
-      <c r="D10">
-        <v>109</v>
-      </c>
-      <c r="E10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>11682</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11">
-        <v>109</v>
-      </c>
-      <c r="E11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>13893</v>
-      </c>
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="D12">
-        <v>109</v>
-      </c>
-      <c r="E12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>24131</v>
-      </c>
-      <c r="B13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-      <c r="D13">
-        <v>309</v>
-      </c>
-      <c r="E13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>24132</v>
-      </c>
-      <c r="B14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="D14">
-        <v>309</v>
-      </c>
-      <c r="E14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>24134</v>
-      </c>
-      <c r="B15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15">
-        <v>2</v>
-      </c>
-      <c r="D15">
-        <v>309</v>
-      </c>
-      <c r="E15" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_702.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_702.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,10 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>بليزو ويفر محشو بالشوكولاتة مغطي بالكراميل و الكرسب و الشوكولاتة بليزو جولد - 10 جنية</t>
-  </si>
-  <si>
-    <t>زيووو اراميش بافس جبنة - 5 جنية</t>
+    <t>حفاضات جود كير مقاس 5 - 40 حفاضة</t>
   </si>
   <si>
     <t>YES</t>
@@ -401,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -429,53 +426,36 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>10816</v>
+        <v>2424</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D2">
-        <v>47</v>
+        <v>865</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>10816</v>
+        <v>2424</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="D3">
-        <v>564</v>
+        <v>173</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>12350</v>
-      </c>
-      <c r="B4" t="s">
         <v>8</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>49.5</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_702.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_702.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,7 +37,10 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>حفاضات جود كير مقاس 5 - 40 حفاضة</t>
+    <t>بريكس مزيل بقع - 30 جم</t>
+  </si>
+  <si>
+    <t>مولفيكس بانتس مقاس 4 - 56 حفاضة</t>
   </si>
   <si>
     <t>YES</t>
@@ -398,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -426,36 +429,53 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>2424</v>
+        <v>12503</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>865</v>
+        <v>145</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>2424</v>
+        <v>23234</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="D3">
-        <v>173</v>
+        <v>930</v>
       </c>
       <c r="E3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>23234</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
+      </c>
+      <c r="C4">
+        <v>25</v>
+      </c>
+      <c r="D4">
+        <v>310</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_702.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_702.xlsx
@@ -37,10 +37,10 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>بريكس مزيل بقع - 30 جم</t>
-  </si>
-  <si>
-    <t>مولفيكس بانتس مقاس 4 - 56 حفاضة</t>
+    <t>لبن جهينة كامل الدسم - 1 لتر</t>
+  </si>
+  <si>
+    <t>ديرى  مثلثات - 8 قطعه</t>
   </si>
   <si>
     <t>YES</t>
@@ -429,7 +429,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>12503</v>
+        <v>248</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -438,7 +438,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>145</v>
+        <v>550</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -446,16 +446,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23234</v>
+        <v>21712</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>930</v>
+        <v>14.25</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -463,16 +463,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23234</v>
+        <v>21712</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>310</v>
+        <v>513</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>

--- a/Pricing Logic/modules/uploads/module_4_702.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_702.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,10 +37,10 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>لبن جهينة كامل الدسم - 1 لتر</t>
-  </si>
-  <si>
-    <t>ديرى  مثلثات - 8 قطعه</t>
+    <t>ستينج فراولة زجاج - 275 مل</t>
+  </si>
+  <si>
+    <t>مناديل بابيا جيب كلاسيك 3 طبقة - 10 باكت</t>
   </si>
   <si>
     <t>YES</t>
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -429,16 +429,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>248</v>
+        <v>1124</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>550</v>
+        <v>158</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -446,35 +446,18 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21712</v>
+        <v>5976</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>14.25</v>
+        <v>182.25</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21712</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>513</v>
-      </c>
-      <c r="E4" t="s">
         <v>9</v>
       </c>
     </row>

--- a/Pricing Logic/modules/uploads/module_4_702.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_702.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,10 +37,10 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>ستينج فراولة زجاج - 275 مل</t>
-  </si>
-  <si>
-    <t>مناديل بابيا جيب كلاسيك 3 طبقة - 10 باكت</t>
+    <t>صابون لوكس بشرة مثالية - 75 جم</t>
+  </si>
+  <si>
+    <t>صابون لوكس بشرة نضرة - 75 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -429,7 +429,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>1124</v>
+        <v>11435</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -438,7 +438,7 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>158</v>
+        <v>60.5</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -446,18 +446,52 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>5976</v>
+        <v>11435</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>182.25</v>
+        <v>484</v>
       </c>
       <c r="E3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>11450</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>59.5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>11450</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>476</v>
+      </c>
+      <c r="E5" t="s">
         <v>9</v>
       </c>
     </row>

--- a/Pricing Logic/modules/uploads/module_4_702.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_702.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="12">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,13 +37,16 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>الأهرام سكر- 1 كجم</t>
-  </si>
-  <si>
-    <t>كوكا كولا جيب - 240 مل</t>
-  </si>
-  <si>
-    <t>تويست بالتوت و جوز الهند - 250 مل</t>
+    <t>فاين بيبى حفاضات دبل لوك ماكس مقاس 5 - 58 حفاضة</t>
+  </si>
+  <si>
+    <t>حفاضات فاين بيبى ماكسى مقاس 4 دبل لوك - 80 حفاضة</t>
+  </si>
+  <si>
+    <t>حفاضات فاين بيبى كبير مقاس 5 دبل لوك - 76 حفاضة</t>
+  </si>
+  <si>
+    <t>فاين سوبر مناديل مطبخ 5+1 رول * 2 طبقة 6 رول</t>
   </si>
   <si>
     <t>YES</t>
@@ -404,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -432,53 +435,121 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>10</v>
+        <v>9239</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D2">
-        <v>262</v>
+        <v>334.75</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>615</v>
+        <v>9239</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D3">
-        <v>287.75</v>
+        <v>1004.25</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19925</v>
+        <v>13258</v>
       </c>
       <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>29</v>
+      </c>
+      <c r="D4">
+        <v>721</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>13258</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>25</v>
+      </c>
+      <c r="D5">
+        <v>360.5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>13259</v>
+      </c>
+      <c r="B6" t="s">
         <v>9</v>
       </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>281.5</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="C6">
+        <v>29</v>
+      </c>
+      <c r="D6">
+        <v>830</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>13259</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>415</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>13274</v>
+      </c>
+      <c r="B8" t="s">
         <v>10</v>
+      </c>
+      <c r="C8">
+        <v>29</v>
+      </c>
+      <c r="D8">
+        <v>226.5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_702.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_702.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="12">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,16 +37,16 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>فاين بيبى حفاضات دبل لوك ماكس مقاس 5 - 58 حفاضة</t>
-  </si>
-  <si>
-    <t>حفاضات فاين بيبى ماكسى مقاس 4 دبل لوك - 80 حفاضة</t>
-  </si>
-  <si>
-    <t>حفاضات فاين بيبى كبير مقاس 5 دبل لوك - 76 حفاضة</t>
-  </si>
-  <si>
-    <t>فاين سوبر مناديل مطبخ 5+1 رول * 2 طبقة 6 رول</t>
+    <t>حلو الشام بسبوسة جوز الهند- 380 جم</t>
+  </si>
+  <si>
+    <t>حلو الشام سحلب كيس - 150 جم</t>
+  </si>
+  <si>
+    <t>حلو الشام نشا -ايزي كوك 240 جم</t>
+  </si>
+  <si>
+    <t>حلو الشام فانيليا  - 2 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -407,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -435,16 +435,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>9239</v>
+        <v>380</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>334.75</v>
+        <v>455</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
@@ -452,16 +452,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>9239</v>
+        <v>10616</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>1004.25</v>
+        <v>360</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -469,16 +469,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>13258</v>
+        <v>12492</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>721</v>
+        <v>340</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
@@ -486,16 +486,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>13258</v>
+        <v>12492</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>360.5</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -503,16 +503,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>13259</v>
+        <v>13324</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>830</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
@@ -520,35 +520,18 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>13259</v>
+        <v>13324</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>415</v>
+        <v>312</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>13274</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8">
-        <v>29</v>
-      </c>
-      <c r="D8">
-        <v>226.5</v>
-      </c>
-      <c r="E8" t="s">
         <v>11</v>
       </c>
     </row>

--- a/Pricing Logic/modules/uploads/module_4_702.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_702.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="33">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,16 +37,79 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>حلو الشام بسبوسة جوز الهند- 380 جم</t>
-  </si>
-  <si>
-    <t>حلو الشام سحلب كيس - 150 جم</t>
-  </si>
-  <si>
-    <t>حلو الشام نشا -ايزي كوك 240 جم</t>
-  </si>
-  <si>
-    <t>حلو الشام فانيليا  - 2 جم</t>
+    <t>شويبس جولد خوخ جيب - 240 مل</t>
+  </si>
+  <si>
+    <t>شويبس يوسفى جيب - 240 مل</t>
+  </si>
+  <si>
+    <t>باندا مثلثات - 8 قطعه</t>
+  </si>
+  <si>
+    <t>باندا مثلثات - 16 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية مثلثات - 8 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية مثلثات - 16 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية جبنة كريمى  بالقشطة - 4 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية جبنة مربعات ب القشطة - 6 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية مربعات جبنة بالقشطة - 8 قطعه</t>
+  </si>
+  <si>
+    <t>ديرى مثلثات - 16 قطعه</t>
+  </si>
+  <si>
+    <t>جبنة باندا فيتا  - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا رومى - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا شيدر - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا رومى - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا شيدر  - 125 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا شيدر - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا بسطرمة  - 125 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا بسطرمة - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا بسطرمة - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة ديرى فيتا بلس  - 125 جم</t>
+  </si>
+  <si>
+    <t>جبنة ديرى فيتا  - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنة ديرى فيتا بلس - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا فيتا 250 جرام</t>
+  </si>
+  <si>
+    <t>جبنة باندا فيتا 125 جرام</t>
+  </si>
+  <si>
+    <t>عرض باندا ( 2علبة باندا250 جم + علبة فول باندا 400جم) - 900 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -407,7 +470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -435,7 +498,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>380</v>
+        <v>5494</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -444,32 +507,32 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>455</v>
+        <v>285</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>10616</v>
+        <v>6931</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>360</v>
+        <v>285</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>12492</v>
+        <v>21704</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
@@ -478,15 +541,15 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>340</v>
+        <v>693</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>12492</v>
+        <v>21704</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
@@ -495,44 +558,503 @@
         <v>3</v>
       </c>
       <c r="D5">
-        <v>85</v>
+        <v>19.25</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>13324</v>
+        <v>21705</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>870</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>13324</v>
+        <v>21705</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
       </c>
       <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>36.25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21706</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8">
+        <v>26.75</v>
+      </c>
+      <c r="E8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21706</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9">
         <v>1</v>
       </c>
-      <c r="D7">
-        <v>312</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
+      <c r="D9">
+        <v>963</v>
+      </c>
+      <c r="E9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21707</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1272</v>
+      </c>
+      <c r="E10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21707</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11">
+        <v>53</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21708</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21708</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1040</v>
+      </c>
+      <c r="E13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21709</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1132.5</v>
+      </c>
+      <c r="E14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21709</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15">
+        <v>37.75</v>
+      </c>
+      <c r="E15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21710</v>
+      </c>
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="D16">
+        <v>49</v>
+      </c>
+      <c r="E16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>21710</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1470</v>
+      </c>
+      <c r="E17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>21713</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>630</v>
+      </c>
+      <c r="E18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>21713</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19">
+        <v>26.25</v>
+      </c>
+      <c r="E19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>21745</v>
+      </c>
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>417.5</v>
+      </c>
+      <c r="E20" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>21752</v>
+      </c>
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>474.25</v>
+      </c>
+      <c r="E21" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>21754</v>
+      </c>
+      <c r="B22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22">
+        <v>417.5</v>
+      </c>
+      <c r="E22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>21771</v>
+      </c>
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23">
+        <v>417.5</v>
+      </c>
+      <c r="E23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>21773</v>
+      </c>
+      <c r="B24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>368.5</v>
+      </c>
+      <c r="E24" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>21774</v>
+      </c>
+      <c r="B25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25">
+        <v>474.25</v>
+      </c>
+      <c r="E25" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>21777</v>
+      </c>
+      <c r="B26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26">
+        <v>368.5</v>
+      </c>
+      <c r="E26" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>21778</v>
+      </c>
+      <c r="B27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27">
+        <v>474.25</v>
+      </c>
+      <c r="E27" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>21779</v>
+      </c>
+      <c r="B28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28">
+        <v>417.5</v>
+      </c>
+      <c r="E28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>21781</v>
+      </c>
+      <c r="B29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29">
+        <v>283</v>
+      </c>
+      <c r="E29" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>21783</v>
+      </c>
+      <c r="B30" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30">
+        <v>356.5</v>
+      </c>
+      <c r="E30" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>21789</v>
+      </c>
+      <c r="B31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+      <c r="D31">
+        <v>310</v>
+      </c>
+      <c r="E31" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>22125</v>
+      </c>
+      <c r="B32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+      <c r="D32">
+        <v>474.25</v>
+      </c>
+      <c r="E32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>22126</v>
+      </c>
+      <c r="B33" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33">
+        <v>368.5</v>
+      </c>
+      <c r="E33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34">
+        <v>25775</v>
+      </c>
+      <c r="B34" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="D34">
+        <v>280</v>
+      </c>
+      <c r="E34" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_702.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_702.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="27">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,7 +37,61 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>نوفي فينجرز شيكولاتة بيضاء - 5 جنية</t>
+    <t>زيت كريستال الممتاز خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال الممتاز خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت قلية خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت قلية خليط - 2.1 لتر</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت صنى خليط عباد الشمس - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت صنى خليط عباد الشمس - 2.4 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس 4 زجاجة - 2.2 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال ذرة 6 زجاجة - 1.6 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس 6 زجاجة - 1.6 لتر</t>
+  </si>
+  <si>
+    <t>سندة زيت خليط - 900 مل</t>
+  </si>
+  <si>
+    <t>سندة زيت خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال ذرة 6 زجاجة - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 1.8 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس 6 زجاجة - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال الممتاز خليط - 2.5 لتر</t>
+  </si>
+  <si>
+    <t>زيت قلية خليط - 4.5 لتر</t>
+  </si>
+  <si>
+    <t>زيت ثمرات خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت ثمرات خليط - 550 مل</t>
   </si>
   <si>
     <t>YES</t>
@@ -398,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -426,7 +480,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21687</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -435,27 +489,316 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>327</v>
+        <v>866</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21687</v>
+        <v>448</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>27.25</v>
+        <v>625</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>470</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>863.5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>471</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>612.25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>1492</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>860</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>2161</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>656</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>2608</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>725.25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>2879</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>810</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>2934</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1066</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>2935</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>892.5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>6496</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>758</v>
+      </c>
+      <c r="E12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>6497</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>855</v>
+      </c>
+      <c r="E13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>7324</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>480.5</v>
+      </c>
+      <c r="E14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>9358</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>554</v>
+      </c>
+      <c r="E15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>11961</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>533.25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>11965</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>705.25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>11968</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1262</v>
+      </c>
+      <c r="E18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>12923</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>855</v>
+      </c>
+      <c r="E19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>12925</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>490</v>
+      </c>
+      <c r="E20" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_702.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_702.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="21">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,61 +37,43 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>زيت كريستال الممتاز خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال الممتاز خليط - 700 مل</t>
-  </si>
-  <si>
-    <t>زيت قلية خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت قلية خليط - 2.1 لتر</t>
-  </si>
-  <si>
-    <t>زيت حبوبة خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت صنى خليط عباد الشمس - 700 مل</t>
-  </si>
-  <si>
-    <t>زيت صنى خليط عباد الشمس - 2.4 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال عباد الشمس 4 زجاجة - 2.2 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال ذرة 6 زجاجة - 1.6 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال عباد الشمس 6 زجاجة - 1.6 لتر</t>
+    <t>زيت حبوبة خليط - 900 مل</t>
+  </si>
+  <si>
+    <t>جبنة دومتى فيتا بلس - 125 جم</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 700 مل</t>
   </si>
   <si>
     <t>سندة زيت خليط - 900 مل</t>
   </si>
   <si>
-    <t>سندة زيت خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال ذرة 6 زجاجة - 700 مل</t>
-  </si>
-  <si>
-    <t>زيت حبوبة خليط - 1.8 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال عباد الشمس 6 زجاجة - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال الممتاز خليط - 2.5 لتر</t>
-  </si>
-  <si>
-    <t>زيت قلية خليط - 4.5 لتر</t>
-  </si>
-  <si>
-    <t>زيت ثمرات خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت ثمرات خليط - 550 مل</t>
+    <t>زيت حبوبة خليط - 2.4 لتر</t>
+  </si>
+  <si>
+    <t>توشيبا احمر ريموت كارت AAA - 4 حجر</t>
+  </si>
+  <si>
+    <t>جبنة دومتى فيتا بلس زيتون - 125 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فيتا بلس - 250 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فيتا بلس - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة دومتي بلس بالزيتون - 500 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة اسطنبولي بلس - 250 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فيتا بلس بسطرمة - 250 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فيتا بلس رومي - 500 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -452,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -480,7 +462,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>9</v>
+        <v>823</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -489,15 +471,15 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>866</v>
+        <v>777</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>448</v>
+        <v>903</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -506,15 +488,15 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>625</v>
+        <v>402</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>470</v>
+        <v>1490</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
@@ -523,15 +505,15 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>863.5</v>
+        <v>620</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>471</v>
+        <v>6496</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
@@ -540,15 +522,15 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>612.25</v>
+        <v>772</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>1492</v>
+        <v>11402</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
@@ -557,248 +539,163 @@
         <v>1</v>
       </c>
       <c r="D6">
-        <v>860</v>
+        <v>717</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>2161</v>
+        <v>12608</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>656</v>
+        <v>370</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>2608</v>
+        <v>12608</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>725.25</v>
+        <v>1850</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>2879</v>
+        <v>13210</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9">
-        <v>810</v>
+        <v>402</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>2934</v>
+        <v>19980</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>1066</v>
+        <v>519</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>2935</v>
+        <v>19981</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>892.5</v>
+        <v>460</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>6496</v>
+        <v>19983</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12">
-        <v>758</v>
+        <v>460</v>
       </c>
       <c r="E12" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>6497</v>
+        <v>19984</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13">
-        <v>855</v>
+        <v>519</v>
       </c>
       <c r="E13" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>7324</v>
+        <v>19988</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>480.5</v>
+        <v>519</v>
       </c>
       <c r="E14" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>9358</v>
+        <v>19991</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15">
-        <v>554</v>
+        <v>460</v>
       </c>
       <c r="E15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>11961</v>
-      </c>
-      <c r="B16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>533.25</v>
-      </c>
-      <c r="E16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>11965</v>
-      </c>
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>705.25</v>
-      </c>
-      <c r="E17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>11968</v>
-      </c>
-      <c r="B18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>1262</v>
-      </c>
-      <c r="E18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>12923</v>
-      </c>
-      <c r="B19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>855</v>
-      </c>
-      <c r="E19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>12925</v>
-      </c>
-      <c r="B20" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>490</v>
-      </c>
-      <c r="E20" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_702.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_702.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,43 +37,10 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>زيت حبوبة خليط - 900 مل</t>
-  </si>
-  <si>
-    <t>جبنة دومتى فيتا بلس - 125 جم</t>
-  </si>
-  <si>
-    <t>زيت حبوبة خليط - 700 مل</t>
-  </si>
-  <si>
-    <t>سندة زيت خليط - 900 مل</t>
-  </si>
-  <si>
-    <t>زيت حبوبة خليط - 2.4 لتر</t>
+    <t>دومتي عصير مانجو- 1 لتر</t>
   </si>
   <si>
     <t>توشيبا احمر ريموت كارت AAA - 4 حجر</t>
-  </si>
-  <si>
-    <t>جبنة دومتى فيتا بلس زيتون - 125 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس - 250 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس - 500 جم</t>
-  </si>
-  <si>
-    <t>جبنة دومتي بلس بالزيتون - 500 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة اسطنبولي بلس - 250 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس بسطرمة - 250 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس رومي - 500 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -434,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -462,240 +429,53 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>823</v>
+        <v>3865</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>777</v>
+        <v>290</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>903</v>
+        <v>12608</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>402</v>
+        <v>370</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>1490</v>
+        <v>12608</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>620</v>
+        <v>1850</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>6496</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>772</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>11402</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>717</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>12608</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>370</v>
-      </c>
-      <c r="E7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>12608</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>1850</v>
-      </c>
-      <c r="E8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>13210</v>
-      </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>402</v>
-      </c>
-      <c r="E9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>19980</v>
-      </c>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10">
-        <v>2</v>
-      </c>
-      <c r="D10">
-        <v>519</v>
-      </c>
-      <c r="E10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19981</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11">
-        <v>460</v>
-      </c>
-      <c r="E11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>19983</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="D12">
-        <v>460</v>
-      </c>
-      <c r="E12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>19984</v>
-      </c>
-      <c r="B13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-      <c r="D13">
-        <v>519</v>
-      </c>
-      <c r="E13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>19988</v>
-      </c>
-      <c r="B14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="D14">
-        <v>519</v>
-      </c>
-      <c r="E14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>19991</v>
-      </c>
-      <c r="B15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15">
-        <v>2</v>
-      </c>
-      <c r="D15">
-        <v>460</v>
-      </c>
-      <c r="E15" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_702.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_702.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,10 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>دومتي عصير مانجو- 1 لتر</t>
-  </si>
-  <si>
-    <t>توشيبا احمر ريموت كارت AAA - 4 حجر</t>
+    <t>كوكا كولا زيرو - 320 مل</t>
   </si>
   <si>
     <t>YES</t>
@@ -401,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -429,7 +426,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>3865</v>
+        <v>4246</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -438,44 +435,10 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>290</v>
+        <v>339</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>12608</v>
-      </c>
-      <c r="B3" t="s">
         <v>8</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>370</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>12608</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1850</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
